--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2017/WASHINGTON_2017.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2017/WASHINGTON_2017.xlsx
@@ -2940,7 +2940,7 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>General Simon Bolivar</t>
+          <t>Gral. Simon Bolivar</t>
         </is>
       </c>
       <c r="C144">
@@ -4884,7 +4884,7 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C252">
@@ -10273,7 +10273,7 @@
         <v>104</v>
       </c>
       <c r="D551">
-        <v>0.009895337773549001</v>
+        <v>0.009895337773549</v>
       </c>
     </row>
     <row r="552">
@@ -13956,7 +13956,7 @@
       </c>
       <c r="B756" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 08 -</t>
+          <t>San Juan Mixtepec -Dto. 08 -</t>
         </is>
       </c>
       <c r="C756">
@@ -13974,7 +13974,7 @@
       </c>
       <c r="B757" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 26 -</t>
+          <t>San Juan Mixtepec -Dto. 26 -</t>
         </is>
       </c>
       <c r="C757">
@@ -14712,7 +14712,7 @@
       </c>
       <c r="B798" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 22 -</t>
+          <t>San Pedro Mixtepec -Dto. 22 -</t>
         </is>
       </c>
       <c r="C798">
